--- a/src/test/fixtures/sample.xlsx
+++ b/src/test/fixtures/sample.xlsx
@@ -808,7 +808,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -867,30 +867,56 @@
         <v>2025-08-09</v>
       </c>
       <c r="B3" t="str">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="C3" t="str">
-        <v>Gamma Gear</v>
+        <v>Alpha Quest</v>
       </c>
       <c r="D3" t="str">
-        <v>https://example.invalid/bid/3</v>
+        <v>https://example.invalid/bid/4</v>
       </c>
       <c r="E3" t="str">
         <v>True</v>
       </c>
       <c r="F3" t="str">
+        <v>False</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2 つ目の投票項目</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-08-09</v>
+      </c>
+      <c r="B4" t="str">
+        <v>103.0</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Gamma Gear</v>
+      </c>
+      <c r="D4" t="str">
+        <v>https://example.invalid/bid/3</v>
+      </c>
+      <c r="E4" t="str">
         <v>True</v>
       </c>
-      <c r="G3" t="str">
+      <c r="F4" t="str">
+        <v>True</v>
+      </c>
+      <c r="G4" t="str">
         <v>目標達成でおまけステージ</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/test/fixtures/sample.xlsx
+++ b/src/test/fixtures/sample.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetData>
     <row r="1">
       <c r="L1" t="str">
@@ -610,48 +610,56 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>11:25</v>
+      </c>
+      <c r="B7" t="str">
+        <v>CM動画再生</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>11:30</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B8" t="str">
         <v>Gamma Gear</v>
       </c>
-      <c r="C7" t="str">
+      <c r="C8" t="str">
         <v>All Levels</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D8" t="str">
         <v>103</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E8" t="str">
         <v>SFC</v>
       </c>
-      <c r="F7" t="str">
+      <c r="F8" t="str">
         <v>会場</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G8" t="str">
         <v>0:25:00</v>
       </c>
-      <c r="H7" t="str">
+      <c r="H8" t="str">
         <v>1</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I8" t="str">
         <v>16x9-1</v>
       </c>
-      <c r="J7" t="str">
+      <c r="J8" t="str">
         <v>1</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K8" t="str">
         <v>1</v>
       </c>
-      <c r="L7" t="str">
+      <c r="L8" t="str">
         <v>runner_d</v>
       </c>
-      <c r="M7" t="str">
+      <c r="M8" t="str">
         <v>disc_d</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U8"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/test/fixtures/sample.xlsx
+++ b/src/test/fixtures/sample.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetData>
     <row r="1">
       <c r="L1" t="str">
@@ -657,9 +657,17 @@
         <v>disc_d</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="B9" t="str">
+        <v>エンディング</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U9"/>
   </ignoredErrors>
 </worksheet>
 </file>
